--- a/iranyitoszamok.xlsx
+++ b/iranyitoszamok.xlsx
@@ -1,86 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3E4FDC-547B-4268-857B-DAE431CB26BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-25515" yWindow="1725" windowWidth="21600" windowHeight="11295" activeTab="8" xr2:uid="{A706BB74-41CC-4D91-8862-76C82B30ADB1}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1. autó " sheetId="1" r:id="rId1"/>
-    <sheet name="2. autó" sheetId="2" r:id="rId2"/>
-    <sheet name="3. autó" sheetId="3" r:id="rId3"/>
-    <sheet name="4. autó" sheetId="4" r:id="rId4"/>
-    <sheet name="5. autó" sheetId="5" r:id="rId5"/>
-    <sheet name="6. autó" sheetId="6" r:id="rId6"/>
-    <sheet name="7. autó" sheetId="7" r:id="rId7"/>
-    <sheet name="8. autó" sheetId="8" r:id="rId8"/>
-    <sheet name="9. autó" sheetId="9" r:id="rId9"/>
+    <sheet name="1. autó" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. autó" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. autó" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. autó" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. autó" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. autó" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. autó" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. autó" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. autó" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="5">
-  <si>
-    <t>Hétfő</t>
-  </si>
-  <si>
-    <t>Kedd</t>
-  </si>
-  <si>
-    <t>Szerda</t>
-  </si>
-  <si>
-    <t>Csütörtök</t>
-  </si>
-  <si>
-    <t>Péntek</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="238"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -98,36 +54,86 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normál" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -137,44 +143,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -201,32 +207,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -253,24 +241,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -282,4048 +252,4195 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FD549E8-F62A-45AE-85EB-DC187053B3C3}">
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>6096</v>
-      </c>
-      <c r="B2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6096</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>6042</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>6077</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>6237</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>6500</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>6050</v>
-      </c>
-      <c r="B3" s="1">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>6050</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>6080</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>6075</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>6238</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>6512</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>6096</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6096</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>6321</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>6211</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>6239</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>6513</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>6090</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>6090</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>6323</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="n">
         <v>6224</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="n">
         <v>6239</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>6528</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>6098</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6098</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>6320</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="n">
         <v>6200</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>6344</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>6521</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6086</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6086</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>6327</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="n">
         <v>6335</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="n">
         <v>6444</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>6522</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>6087</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6087</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>6085</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="n">
         <v>6328</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="n">
         <v>6348</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>6527</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>6088</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>6088</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>6221</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" t="n">
         <v>6333</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" t="n">
         <v>6345</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" t="n">
         <v>6523</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>6097</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>6223</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" t="n">
         <v>6332</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" t="n">
         <v>6353</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" t="n">
         <v>6524</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>6043</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6043</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>6070</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" t="n">
         <v>6300</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" t="n">
         <v>6352</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" t="n">
         <v>6525</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6041</v>
-      </c>
-      <c r="B12" s="1">
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6041</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>6076</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" t="n">
         <v>6351</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" t="n">
         <v>6346</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" t="n">
         <v>6511</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>6085</v>
-      </c>
-      <c r="B13" s="1">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="n">
         <v>6035</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" t="n">
         <v>6343</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" t="n">
         <v>6347</v>
       </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1">
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
         <v>6222</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" t="n">
         <v>6342</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
         <v>6341</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
         <v>6311</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
         <v>6336</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
         <v>6337</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{569FE275-BEC1-4A25-8017-63026FF3F1AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>6078</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>6400</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>6033</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>6120</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>6440</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>6114</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" t="n">
         <v>6136</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>6115</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>6134</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>6445</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>6132</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" t="n">
         <v>6413</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>6100</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>6135</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>6446</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>6235</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" t="n">
         <v>6412</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="n">
         <v>6113</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="n">
         <v>6411</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>6449</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>6230</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="n">
         <v>6422</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="n">
         <v>6765</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>6785</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>6451</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>6236</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" t="n">
         <v>6423</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="n">
         <v>6133</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="n">
         <v>6786</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>6452</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>6131</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" t="n">
         <v>6421</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="n">
         <v>6116</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="n">
         <v>6783</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>6447</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>6414</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>6784</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" t="n">
         <v>6448</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
         <v>6782</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" t="n">
         <v>6453</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
         <v>6758</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" t="n">
         <v>6454</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
         <v>6781</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" t="n">
         <v>6455</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
         <v>6787</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" t="n">
         <v>6456</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
         <v>6795</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" t="n">
         <v>6435</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
         <v>6794</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" t="n">
         <v>6424</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
         <v>6792</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" t="n">
         <v>6430</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
         <v>6793</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" t="n">
         <v>6425</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F87039C-CF5B-4BB7-B849-8DCECAE396E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>6060</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>5900</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>6612</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>6800</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>6772</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>6031</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" t="n">
         <v>6821</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>6600</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>6922</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>6754</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>6065</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" t="n">
         <v>6622</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>6635</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>6923</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>6756</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>6066</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" t="n">
         <v>6621</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="n">
         <v>6630</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="n">
         <v>6750</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>6755</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>6064</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="n">
         <v>6623</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="n">
         <v>6636</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>6762</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>6773</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>6032</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" t="n">
         <v>6625</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="n">
         <v>6766</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="n">
         <v>6763</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>6774</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>6111</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" t="n">
         <v>5932</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="n">
         <v>6764</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="n">
         <v>6921</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>6932</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>6648</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" t="n">
         <v>6624</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" t="n">
         <v>6767</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
         <v>6775</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" t="n">
         <v>6645</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="n">
         <v>6769</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
         <v>6900</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" t="n">
         <v>6647</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="n">
         <v>6678</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
         <v>6931</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12">
+      <c r="A12" t="n">
         <v>6646</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="n">
         <v>6760</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
         <v>6932</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" t="n">
         <v>6112</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
         <v>6933</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" t="n">
         <v>6640</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
         <v>6912</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1">
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
         <v>6913</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1">
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
         <v>6911</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
         <v>6722</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="1">
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
         <v>6723</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="1">
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
         <v>6724</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69581654-8B38-442C-A154-EC4AB8D1E6A7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>5502</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>5700</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>5600</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>5919</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>5712</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>5561</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" t="n">
         <v>5624</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>5675</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>5945</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>5925</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>5540</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" t="n">
         <v>5630</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>5920</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>5946</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>5661</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>5551</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" t="n">
         <v>5673</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
         <v>5940</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>5609</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>5552</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="n">
         <v>5672</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
         <v>6917</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>5662</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>5553</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" t="n">
         <v>5650</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
         <v>6914</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>5665</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>5674</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" t="n">
         <v>5622</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
         <v>6915</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>5664</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>5556</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" t="n">
         <v>5643</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>6916</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" t="n">
         <v>5667</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" t="n">
         <v>5555</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" t="n">
         <v>5641</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
         <v>6917</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" t="n">
         <v>5752</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" t="n">
         <v>5621</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" t="n">
         <v>5530</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
         <v>5820</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" t="n">
         <v>5746</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="n">
         <v>5536</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
         <v>5811</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" t="n">
         <v>5745</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1">
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="n">
         <v>5534</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
         <v>5800</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" t="n">
         <v>5751</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1">
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="n">
         <v>5731</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
         <v>5668</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" t="n">
         <v>5743</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1">
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
         <v>5720</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
         <v>5830</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" t="n">
         <v>5742</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1">
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="n">
         <v>5726</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
         <v>5837</v>
       </c>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1">
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="n">
         <v>5727</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
         <v>5838</v>
       </c>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1">
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="n">
         <v>5732</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="n">
         <v>5537</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
         <v>5836</v>
       </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1">
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="n">
         <v>5725</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="n">
         <v>5732</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="n">
         <v>5539</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="n">
         <v>5538</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A346B2E9-CE40-467D-9FB9-76E6C54316F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>9361</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>9168</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>9461</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>9730</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>9794</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>9371</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" t="n">
         <v>9311</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>9471</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>9739</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>9900</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>9441</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" t="n">
         <v>9300</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>9733</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>9721</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>9909</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>9433</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" t="n">
         <v>9351</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="n">
         <v>9740</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="n">
         <v>9743</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>9921</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>9451</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="n">
         <v>9321</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="n">
         <v>9632</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>9751</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>9781</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>9481</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" t="n">
         <v>9341</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="n">
         <v>9662</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="n">
         <v>9611</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>9771</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>9421</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" t="n">
         <v>9363</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="n">
         <v>9621</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="n">
         <v>9789</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>9912</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>9492</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" t="n">
         <v>9344</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" t="n">
         <v>9641</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" t="n">
         <v>9722</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" t="n">
         <v>9757</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" t="n">
         <v>9362</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" t="n">
         <v>9512</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" t="n">
         <v>9631</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" t="n">
         <v>9723</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" t="n">
         <v>9761</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" t="n">
         <v>9372</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" t="n">
         <v>9643</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" t="n">
         <v>9621</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" t="n">
         <v>9724</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" t="n">
         <v>9795</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12">
+      <c r="A12" t="n">
         <v>9373</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" t="n">
         <v>9651</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" t="n">
         <v>9462</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" t="n">
         <v>9725</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" t="n">
         <v>9796</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" t="n">
         <v>9442</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" t="n">
         <v>9661</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" t="n">
         <v>9463</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" t="n">
         <v>9726</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" t="n">
         <v>9798</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" t="n">
         <v>9443</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" t="n">
         <v>9664</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" t="n">
         <v>9464</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" t="n">
         <v>9727</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" t="n">
         <v>9922</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15">
+      <c r="A15" t="n">
         <v>9444</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" t="n">
         <v>9375</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" t="n">
         <v>9472</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" t="n">
         <v>9744</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" t="n">
         <v>9782</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16">
+      <c r="A16" t="n">
         <v>9434</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" t="n">
         <v>9169</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" t="n">
         <v>9473</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" t="n">
         <v>9745</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" t="n">
         <v>9783</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17">
+      <c r="A17" t="n">
         <v>9435</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" t="n">
         <v>9312</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" t="n">
         <v>9474</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" t="n">
         <v>9746</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" t="n">
         <v>9784</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18">
+      <c r="A18" t="n">
         <v>9436</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" t="n">
         <v>9313</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" t="n">
         <v>9475</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" t="n">
         <v>9747</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" t="n">
         <v>9772</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19">
+      <c r="A19" t="n">
         <v>9437</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" t="n">
         <v>9352</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" t="n">
         <v>9476</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" t="n">
         <v>9748</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" t="n">
         <v>9773</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20">
+      <c r="A20" t="n">
         <v>9482</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" t="n">
         <v>9353</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" t="n">
         <v>9734</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" t="n">
         <v>9749</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" t="n">
         <v>9774</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21">
+      <c r="A21" t="n">
         <v>9483</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" t="n">
         <v>9354</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" t="n">
         <v>9735</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" t="n">
         <v>9752</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" t="n">
         <v>9775</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22">
+      <c r="A22" t="n">
         <v>9484</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" t="n">
         <v>9322</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" t="n">
         <v>9736</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" t="n">
         <v>9753</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" t="n">
         <v>9776</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23">
+      <c r="A23" t="n">
         <v>9485</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" t="n">
         <v>9323</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" t="n">
         <v>9737</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" t="n">
         <v>9754</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" t="n">
         <v>9777</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24">
+      <c r="A24" t="n">
         <v>9422</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" t="n">
         <v>9324</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" t="n">
         <v>9738</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" t="n">
         <v>9612</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" t="n">
         <v>9762</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25">
+      <c r="A25" t="n">
         <v>9423</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" t="n">
         <v>9325</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" t="n">
         <v>9633</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" t="n">
         <v>9790</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" t="n">
         <v>9763</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26">
+      <c r="A26" t="n">
         <v>9493</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" t="n">
         <v>9326</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" t="n">
         <v>9634</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" t="n">
         <v>9791</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" t="n">
         <v>9764</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="27">
+      <c r="A27" t="n">
         <v>9494</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" t="n">
         <v>9341</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" t="n">
         <v>9635</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" t="n">
         <v>9792</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" t="n">
         <v>9765</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+    <row r="28">
+      <c r="A28" t="n">
         <v>9495</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" t="n">
         <v>9342</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" t="n">
         <v>9636</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" t="n">
         <v>9793</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" t="n">
         <v>9766</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+    <row r="29">
+      <c r="A29" t="n">
         <v>9330</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" t="n">
         <v>9343</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" t="n">
         <v>9663</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>9400</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" t="n">
         <v>9344</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" t="n">
         <v>9622</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="n">
         <v>9345</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" t="n">
         <v>9623</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="n">
         <v>9346</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" t="n">
         <v>9624</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="n">
         <v>9364</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" t="n">
         <v>9625</v>
       </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="n">
         <v>9365</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" t="n">
         <v>9632</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="n">
         <v>9513</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" t="n">
         <v>9633</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="n">
         <v>9514</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" t="n">
         <v>9634</v>
       </c>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1">
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="n">
         <v>9515</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" t="n">
         <v>9635</v>
       </c>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1">
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="n">
         <v>9652</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" t="n">
         <v>9636</v>
       </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1">
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="n">
         <v>9653</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" t="n">
         <v>9622</v>
       </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1">
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="n">
         <v>9665</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7087A44-D739-4718-AF07-995336FDFC22}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>9171</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" t="n">
         <v>9000</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>9700</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>9091</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>9144</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>5141</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" t="n">
         <v>9062</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
         <v>9082</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>9142</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4">
+      <c r="A4" t="n">
         <v>9143</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" t="n">
         <v>9063</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
         <v>9111</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>9145</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5">
+      <c r="A5" t="n">
         <v>9161</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" t="n">
         <v>9081</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
         <v>9112</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>9100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6">
+      <c r="A6" t="n">
         <v>9153</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" t="n">
         <v>9086</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
         <v>9123</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>9131</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7">
+      <c r="A7" t="n">
         <v>9181</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" t="n">
         <v>9071</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
         <v>8431</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>9121</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8">
+      <c r="A8" t="n">
         <v>9200</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" t="n">
         <v>9072</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
         <v>8553</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>9314</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9">
+      <c r="A9" t="n">
         <v>9231</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" t="n">
         <v>9073</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
         <v>8563</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" t="n">
         <v>9316</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10">
+      <c r="A10" t="n">
         <v>9241</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
         <v>8571</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" t="n">
         <v>9315</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11">
+      <c r="A11" t="n">
         <v>9221</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
         <v>9092</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" t="n">
         <v>8516</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12">
+      <c r="A12" t="n">
         <v>9172</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1">
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
         <v>9093</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" t="n">
         <v>8518</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" t="n">
         <v>9173</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1">
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
         <v>9094</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" t="n">
         <v>8533</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" t="n">
         <v>9174</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1">
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
         <v>9095</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" t="n">
         <v>8521</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15">
+      <c r="A15" t="n">
         <v>9175</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
         <v>9096</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" t="n">
         <v>8541</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16">
+      <c r="A16" t="n">
         <v>9176</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
         <v>9097</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" t="n">
         <v>9132</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17">
+      <c r="A17" t="n">
         <v>9177</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1">
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
         <v>9098</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" t="n">
         <v>9133</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18">
+      <c r="A18" t="n">
         <v>9178</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1">
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
         <v>9099</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" t="n">
         <v>9134</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19">
+      <c r="A19" t="n">
         <v>9162</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="n">
         <v>9083</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" t="n">
         <v>9135</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20">
+      <c r="A20" t="n">
         <v>9163</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1">
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="n">
         <v>9084</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" t="n">
         <v>9136</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21">
+      <c r="A21" t="n">
         <v>9164</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1">
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="n">
         <v>9085</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" t="n">
         <v>9122</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22">
+      <c r="A22" t="n">
         <v>9165</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1">
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="n">
         <v>8432</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" t="n">
         <v>9123</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23">
+      <c r="A23" t="n">
         <v>9166</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1">
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="n">
         <v>8433</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" t="n">
         <v>9124</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24">
+      <c r="A24" t="n">
         <v>9167</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1">
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="n">
         <v>8434</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" t="n">
         <v>9125</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25">
+      <c r="A25" t="n">
         <v>9168</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1">
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
         <v>8435</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" t="n">
         <v>8522</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26">
+      <c r="A26" t="n">
         <v>9182</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1">
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
         <v>8436</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" t="n">
         <v>8523</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+    <row r="27">
+      <c r="A27" t="n">
         <v>9183</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="n">
         <v>8437</v>
       </c>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>9184</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
         <v>8438</v>
       </c>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>9232</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
         <v>8439</v>
       </c>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>9233</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="n">
         <v>8554</v>
       </c>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>9234</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
         <v>8555</v>
       </c>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>9235</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
         <v>8556</v>
       </c>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>9242</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
         <v>8557</v>
       </c>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>9243</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
         <v>8558</v>
       </c>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>9244</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1">
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
         <v>8564</v>
       </c>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>9245</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>9246</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>9222</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>9223</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>9224</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>9225</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>9226</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34D05FA6-03F4-4FB6-BA55-C8A848DFC775}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>9951</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>9944</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>8943</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>8946</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>8824</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>9917</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" t="n">
         <v>9938</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>8983</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>8951</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>8855</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>9931</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" t="n">
         <v>8969</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>8989</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>8876</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>8800</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>8999</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" t="n">
         <v>8960</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="n">
         <v>8911</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="n">
         <v>8885</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>8832</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>9961</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="n">
         <v>8981</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="n">
         <v>8921</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>8893</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>8881</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>9970</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" t="n">
         <v>8919</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="n">
         <v>9811</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="n">
         <v>8771</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>8861</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>9982</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" t="n">
         <v>8990</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="n">
         <v>9826</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="n">
         <v>8947</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>8825</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>9941</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" t="n">
         <v>8945</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" t="n">
         <v>9913</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" t="n">
         <v>8952</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" t="n">
         <v>8826</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" t="n">
         <v>9952</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" t="n">
         <v>8947</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" t="n">
         <v>8944</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" t="n">
         <v>8953</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" t="n">
         <v>8827</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" t="n">
         <v>9953</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" t="n">
         <v>9945</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" t="n">
         <v>8990</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" t="n">
         <v>8954</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" t="n">
         <v>8856</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12">
+      <c r="A12" t="n">
         <v>9954</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" t="n">
         <v>9946</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" t="n">
         <v>8991</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" t="n">
         <v>8955</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" t="n">
         <v>8857</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" t="n">
         <v>9918</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" t="n">
         <v>8970</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" t="n">
         <v>8992</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" t="n">
         <v>8956</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" t="n">
         <v>8833</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" t="n">
         <v>9919</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" t="n">
         <v>8971</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" t="n">
         <v>8993</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" t="n">
         <v>8957</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" t="n">
         <v>8834</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15">
+      <c r="A15" t="n">
         <v>9932</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" t="n">
         <v>8972</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" t="n">
         <v>8994</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" t="n">
         <v>8958</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" t="n">
         <v>8835</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16">
+      <c r="A16" t="n">
         <v>9933</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" t="n">
         <v>8973</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" t="n">
         <v>8995</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" t="n">
         <v>8959</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" t="n">
         <v>8882</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17">
+      <c r="A17" t="n">
         <v>9934</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" t="n">
         <v>8974</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" t="n">
         <v>8996</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" t="n">
         <v>8877</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" t="n">
         <v>8883</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18">
+      <c r="A18" t="n">
         <v>9935</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" t="n">
         <v>8975</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" t="n">
         <v>8997</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" t="n">
         <v>8878</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" t="n">
         <v>8862</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19">
+      <c r="A19" t="n">
         <v>9936</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" t="n">
         <v>8976</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" t="n">
         <v>8998</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" t="n">
         <v>8879</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" t="n">
         <v>8863</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20">
+      <c r="A20" t="n">
         <v>9937</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" t="n">
         <v>8977</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" t="n">
         <v>8912</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" t="n">
         <v>8886</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" t="n">
         <v>8864</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21">
+      <c r="A21" t="n">
         <v>9962</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" t="n">
         <v>8978</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" t="n">
         <v>8913</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" t="n">
         <v>8887</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" t="n">
         <v>8865</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22">
+      <c r="A22" t="n">
         <v>9983</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" t="n">
         <v>8982</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" t="n">
         <v>8914</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" t="n">
         <v>8888</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" t="n">
         <v>8866</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23">
+      <c r="A23" t="n">
         <v>9942</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" t="n">
         <v>8983</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" t="n">
         <v>9812</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" t="n">
         <v>8889</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" t="n">
         <v>8867</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24">
+      <c r="A24" t="n">
         <v>9943</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" t="n">
         <v>8984</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" t="n">
         <v>9813</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" t="n">
         <v>8894</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" t="n">
         <v>8868</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1">
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="n">
         <v>8985</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" t="n">
         <v>9814</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" t="n">
         <v>8895</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" t="n">
         <v>8869</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="n">
         <v>8986</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" t="n">
         <v>9914</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" t="n">
         <v>8896</v>
       </c>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1">
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="n">
         <v>8987</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" t="n">
         <v>9915</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="n">
         <v>8988</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="n">
         <v>8948</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53DEC08A-3F37-4261-B7B2-2BAA035A3C8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>8752</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>8943</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>8932</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>8900</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>9800</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>8756</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" t="n">
         <v>8925</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>8934</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>8921</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>9821</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>8821</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" t="n">
         <v>8929</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>8785</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>8923</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>9831</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>8827</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" t="n">
         <v>8935</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="n">
         <v>8788</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="n">
         <v>8931</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>9833</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>8742</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="n">
         <v>8915</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="n">
         <v>8351</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>8913</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>8941</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>8391</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" t="n">
         <v>8762</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="n">
         <v>8321</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="n">
         <v>8924</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>9600</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>8936</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" t="n">
         <v>8741</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="n">
         <v>8792</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="n">
         <v>8914</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>9756</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>8761</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" t="n">
         <v>8782</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" t="n">
         <v>8330</v>
       </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1">
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
         <v>9681</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" t="n">
         <v>8771</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" t="n">
         <v>8380</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" t="n">
         <v>9549</v>
       </c>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1">
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
         <v>9674</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" t="n">
         <v>8753</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" t="n">
         <v>8354</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" t="n">
         <v>8341</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1">
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
         <v>9822</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12">
+      <c r="A12" t="n">
         <v>8743</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" t="n">
         <v>8360</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" t="n">
         <v>8352</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
         <v>9823</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" t="n">
         <v>8744</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" t="n">
         <v>8372</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" t="n">
         <v>8353</v>
       </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1">
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
         <v>9824</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" t="n">
         <v>8745</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" t="n">
         <v>8311</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" t="n">
         <v>354</v>
       </c>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1">
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
         <v>9825</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15">
+      <c r="A15" t="n">
         <v>8746</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" t="n">
         <v>8926</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" t="n">
         <v>8355</v>
       </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1">
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
         <v>9834</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16">
+      <c r="A16" t="n">
         <v>8748</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" t="n">
         <v>8783</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" t="n">
         <v>8356</v>
       </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1">
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
         <v>9835</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17">
+      <c r="A17" t="n">
         <v>8749</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" t="n">
         <v>8784</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" t="n">
         <v>8357</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1">
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
         <v>9836</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18">
+      <c r="A18" t="n">
         <v>8848</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" t="n">
         <v>8373</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" t="n">
         <v>8793</v>
       </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
         <v>8942</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19">
+      <c r="A19" t="n">
         <v>8392</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" t="n">
         <v>8312</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" t="n">
         <v>8794</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1">
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
         <v>9682</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20">
+      <c r="A20" t="n">
         <v>8762</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" t="n">
         <v>8313</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" t="n">
         <v>8795</v>
       </c>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1">
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
         <v>9683</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21">
+      <c r="A21" t="n">
         <v>8763</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" t="n">
         <v>8314</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" t="n">
         <v>8796</v>
       </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
         <v>9684</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22">
+      <c r="A22" t="n">
         <v>8764</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" t="n">
         <v>8315</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" t="n">
         <v>8797</v>
       </c>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1">
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="n">
         <v>9685</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23">
+      <c r="A23" t="n">
         <v>8765</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" t="n">
         <v>8316</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" t="n">
         <v>8798</v>
       </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1">
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="n">
         <v>9686</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24">
+      <c r="A24" t="n">
         <v>8766</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" t="n">
         <v>8317</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" t="n">
         <v>8799</v>
       </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1">
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
         <v>9675</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25">
+      <c r="A25" t="n">
         <v>8767</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" t="n">
         <v>8318</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" t="n">
         <v>8342</v>
       </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1">
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
         <v>9676</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26">
+      <c r="A26" t="n">
         <v>8768</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" t="n">
         <v>8319</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" t="n">
         <v>8343</v>
       </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>8769</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1">
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="n">
         <v>8344</v>
       </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>8772</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1">
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="n">
         <v>8345</v>
       </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>8773</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="n">
         <v>8346</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>8774</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="n">
         <v>8347</v>
       </c>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>8775</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1">
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="n">
         <v>8348</v>
       </c>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>8776</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1">
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
         <v>8349</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>8777</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>8778</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>8779</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D9ABF8-15AE-4F64-9C81-D68E18D9E766}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Hétfő</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Kedd</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Szerda</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Csütörtök</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Péntek</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>8261</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" t="n">
         <v>8475</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" t="n">
         <v>9523</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" t="n">
         <v>8200</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="n">
         <v>8440</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="3">
+      <c r="A3" t="n">
         <v>8300</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" t="n">
         <v>8348</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" t="n">
         <v>9533</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" t="n">
         <v>8246</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="n">
         <v>8581</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+    <row r="4">
+      <c r="A4" t="n">
         <v>8251</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" t="n">
         <v>9541</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" t="n">
         <v>8500</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" t="n">
         <v>8226</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="n">
         <v>8420</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+    <row r="5">
+      <c r="A5" t="n">
         <v>8237</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" t="n">
         <v>9673</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" t="n">
         <v>8512</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" t="n">
         <v>8220</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" t="n">
         <v>8109</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+    <row r="6">
+      <c r="A6" t="n">
         <v>8241</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" t="n">
         <v>9551</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" t="n">
         <v>8514</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" t="n">
         <v>8171</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" t="n">
         <v>8413</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="7">
+      <c r="A7" t="n">
         <v>8271</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" t="n">
         <v>8491</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" t="n">
         <v>8591</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" t="n">
         <v>8161</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" t="n">
         <v>8441</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="8">
+      <c r="A8" t="n">
         <v>8281</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" t="n">
         <v>9561</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" t="n">
         <v>8481</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" t="n">
         <v>9191</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" t="n">
         <v>8442</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9">
+      <c r="A9" t="n">
         <v>8291</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" t="n">
         <v>9531</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" t="n">
         <v>8447</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" t="n">
         <v>8191</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" t="n">
         <v>8443</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+    <row r="10">
+      <c r="A10" t="n">
         <v>8308</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" t="n">
         <v>9511</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" t="n">
         <v>8455</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" t="n">
         <v>8105</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" t="n">
         <v>8444</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11">
+      <c r="A11" t="n">
         <v>8452</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" t="n">
         <v>9516</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" t="n">
         <v>8471</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" t="n">
         <v>8100</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" t="n">
         <v>8445</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+    <row r="12">
+      <c r="A12" t="n">
         <v>8409</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" t="n">
         <v>9522</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" t="n">
         <v>8460</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" t="n">
         <v>8247</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" t="n">
         <v>8446</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+    <row r="13">
+      <c r="A13" t="n">
         <v>8262</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" t="n">
         <v>8476</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" t="n">
         <v>8478</v>
       </c>
-      <c r="D13" s="1">
+      <c r="D13" t="n">
         <v>8248</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" t="n">
         <v>8421</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+    <row r="14">
+      <c r="A14" t="n">
         <v>8263</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" t="n">
         <v>8477</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" t="n">
         <v>8468</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" t="n">
         <v>8227</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" t="n">
         <v>8422</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+    <row r="15">
+      <c r="A15" t="n">
         <v>8264</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" t="n">
         <v>9542</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" t="n">
         <v>9534</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" t="n">
         <v>8228</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" t="n">
         <v>8423</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+    <row r="16">
+      <c r="A16" t="n">
         <v>8265</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" t="n">
         <v>9543</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" t="n">
         <v>9535</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" t="n">
         <v>8229</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" t="n">
         <v>8424</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17">
+      <c r="A17" t="n">
         <v>8252</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" t="n">
         <v>9544</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" t="n">
         <v>8515</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" t="n">
         <v>8230</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" t="n">
         <v>8425</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+    <row r="18">
+      <c r="A18" t="n">
         <v>8253</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" t="n">
         <v>9545</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" t="n">
         <v>8592</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" t="n">
         <v>8231</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" t="n">
         <v>8426</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19">
+      <c r="A19" t="n">
         <v>8254</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" t="n">
         <v>9546</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" t="n">
         <v>8593</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" t="n">
         <v>8232</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" t="n">
         <v>8427</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+    <row r="20">
+      <c r="A20" t="n">
         <v>8255</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" t="n">
         <v>9547</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" t="n">
         <v>8594</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D20" t="n">
         <v>8233</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" t="n">
         <v>8428</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+    <row r="21">
+      <c r="A21" t="n">
         <v>8256</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" t="n">
         <v>9552</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" t="n">
         <v>8596</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" t="n">
         <v>8172</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" t="n">
         <v>8429</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+    <row r="22">
+      <c r="A22" t="n">
         <v>8242</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" t="n">
         <v>9553</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" t="n">
         <v>8597</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" t="n">
         <v>8173</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" t="n">
         <v>8414</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+    <row r="23">
+      <c r="A23" t="n">
         <v>8243</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" t="n">
         <v>9554</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" t="n">
         <v>8482</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" t="n">
         <v>8174</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" t="n">
         <v>8415</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+    <row r="24">
+      <c r="A24" t="n">
         <v>8244</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" t="n">
         <v>9555</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" t="n">
         <v>8483</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" t="n">
         <v>8175</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" t="n">
         <v>8416</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+    <row r="25">
+      <c r="A25" t="n">
         <v>8245</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" t="n">
         <v>9556</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" t="n">
         <v>8484</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" t="n">
         <v>8162</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" t="n">
         <v>8417</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+    <row r="26">
+      <c r="A26" t="n">
         <v>8272</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" t="n">
         <v>8492</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" t="n">
         <v>8485</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" t="n">
         <v>9192</v>
       </c>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>8273</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" t="n">
         <v>8493</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" t="n">
         <v>8448</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" t="n">
         <v>8192</v>
       </c>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>8274</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" t="n">
         <v>8494</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" t="n">
         <v>8449</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28" t="n">
         <v>8193</v>
       </c>
-      <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
         <v>8275</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" t="n">
         <v>8495</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" t="n">
         <v>8456</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" t="n">
         <v>8194</v>
       </c>
-      <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>8282</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" t="n">
         <v>8496</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" t="n">
         <v>8457</v>
       </c>
-      <c r="D30" s="1">
+      <c r="D30" t="n">
         <v>8195</v>
       </c>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
         <v>8283</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" t="n">
         <v>8497</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" t="n">
         <v>8458</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" t="n">
         <v>8196</v>
       </c>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
         <v>8284</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" t="n">
         <v>9532</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" t="n">
         <v>8472</v>
       </c>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
         <v>8285</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" t="n">
         <v>9517</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" t="n">
         <v>8473</v>
       </c>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>8286</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
         <v>8474</v>
       </c>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>8292</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1">
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
         <v>8479</v>
       </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
         <v>8293</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
         <v>8294</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>8295</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>8296</v>
       </c>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
         <v>8297</v>
       </c>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>8453</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
         <v>8454</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/iranyitoszamok.xlsx
+++ b/iranyitoszamok.xlsx
@@ -1,42 +1,117 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="1. autó" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="2. autó" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="3. autó" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="4. autó" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="5. autó" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="6. autó" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="7. autó" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="8. autó" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="9. autó" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1. autó" sheetId="1" r:id="rId1"/>
+    <sheet name="2. autó" sheetId="2" r:id="rId2"/>
+    <sheet name="3. autó" sheetId="3" r:id="rId3"/>
+    <sheet name="4. autó" sheetId="4" r:id="rId4"/>
+    <sheet name="5. autó" sheetId="5" r:id="rId5"/>
+    <sheet name="6. autó" sheetId="6" r:id="rId6"/>
+    <sheet name="7. autó" sheetId="7" r:id="rId7"/>
+    <sheet name="8. autó" sheetId="8" r:id="rId8"/>
+    <sheet name="9. autó" sheetId="9" r:id="rId9"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="24">
+  <si>
+    <t>Hétfő</t>
+  </si>
+  <si>
+    <t>Kedd</t>
+  </si>
+  <si>
+    <t>Szerda</t>
+  </si>
+  <si>
+    <t>Csütörtök</t>
+  </si>
+  <si>
+    <t>Péntek</t>
+  </si>
+  <si>
+    <t>6096</t>
+  </si>
+  <si>
+    <t>6050</t>
+  </si>
+  <si>
+    <t>6090</t>
+  </si>
+  <si>
+    <t>6098</t>
+  </si>
+  <si>
+    <t>6086</t>
+  </si>
+  <si>
+    <t>6087</t>
+  </si>
+  <si>
+    <t>6088</t>
+  </si>
+  <si>
+    <t>6097</t>
+  </si>
+  <si>
+    <t>6043</t>
+  </si>
+  <si>
+    <t>6041</t>
+  </si>
+  <si>
+    <t>6085</t>
+  </si>
+  <si>
+    <t>6078</t>
+  </si>
+  <si>
+    <t>6114</t>
+  </si>
+  <si>
+    <t>6132</t>
+  </si>
+  <si>
+    <t>6235</t>
+  </si>
+  <si>
+    <t>6230</t>
+  </si>
+  <si>
+    <t>6236</t>
+  </si>
+  <si>
+    <t>6131</t>
+  </si>
+  <si>
+    <t>6414</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -55,80 +130,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -416,4031 +424,3513 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
         <v>6042</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>6077</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>6237</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>6500</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>6050</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
         <v>6080</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>6075</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>6238</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>6512</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>6096</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
         <v>6321</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>6211</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>6239</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>6513</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>6090</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
         <v>6323</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>6224</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>6239</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>6528</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6098</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
         <v>6320</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6200</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>6344</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>6521</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>6086</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
         <v>6327</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>6335</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>6444</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>6522</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6087</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8">
         <v>6085</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>6328</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>6348</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>6527</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6088</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
         <v>6221</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>6333</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>6345</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>6523</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>6097</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10">
         <v>6223</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>6332</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>6353</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>6524</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>6043</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
         <v>6070</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>6300</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>6352</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>6525</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>6041</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
         <v>6076</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>6351</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>6346</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>6511</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
         <v>6035</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>6343</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>6347</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="n">
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14">
         <v>6222</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>6342</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
+    </row>
+    <row r="15" spans="1:5">
+      <c r="C15">
         <v>6341</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
+    </row>
+    <row r="16" spans="1:5">
+      <c r="C16">
         <v>6311</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17">
         <v>6336</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="n">
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18">
         <v>6337</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>6078</v>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2">
         <v>6400</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>6033</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>6120</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>6440</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>6114</v>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
         <v>6136</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>6115</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>6134</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>6445</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>6132</v>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
         <v>6413</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>6100</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>6135</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>6446</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>6235</v>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
         <v>6412</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>6113</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>6411</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>6449</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6230</v>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6">
         <v>6422</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6765</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>6785</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>6451</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6236</v>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7">
         <v>6423</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>6133</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>6786</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>6452</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6131</v>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
         <v>6421</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>6116</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>6783</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>6447</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>6414</v>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
         <v>6784</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>6448</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
+    <row r="10" spans="1:5">
+      <c r="D10">
         <v>6782</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>6453</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
+    <row r="11" spans="1:5">
+      <c r="D11">
         <v>6758</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>6454</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
+    <row r="12" spans="1:5">
+      <c r="D12">
         <v>6781</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>6455</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
+    <row r="13" spans="1:5">
+      <c r="D13">
         <v>6787</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>6456</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
+    <row r="14" spans="1:5">
+      <c r="D14">
         <v>6795</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>6435</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
+    <row r="15" spans="1:5">
+      <c r="D15">
         <v>6794</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>6424</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
+    <row r="16" spans="1:5">
+      <c r="D16">
         <v>6792</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>6430</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
+    <row r="17" spans="4:5">
+      <c r="D17">
         <v>6793</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>6425</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6085</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>6060</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>5900</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>6612</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>6800</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>6772</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>6031</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>6821</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>6600</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>6922</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>6754</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>6065</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>6622</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>6635</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>6923</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>6756</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>6066</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>6621</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>6630</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>6750</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>6755</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>6064</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>6623</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>6636</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>6762</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>6773</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>6032</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>6625</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>6766</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>6763</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>6774</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>6111</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>5932</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>6764</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>6921</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>6932</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>6648</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>6624</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>6767</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>6775</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>6645</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>6769</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>6900</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>6647</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>6678</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>6931</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12">
         <v>6646</v>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>6760</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>6932</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13">
         <v>6112</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>6933</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14">
         <v>6640</v>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>6912</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
+    <row r="15" spans="1:5">
+      <c r="E15">
         <v>6913</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
+    <row r="16" spans="1:5">
+      <c r="E16">
         <v>6911</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
+    <row r="17" spans="5:5">
+      <c r="E17">
         <v>6722</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
+    <row r="18" spans="5:5">
+      <c r="E18">
         <v>6723</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
+    <row r="19" spans="5:5">
+      <c r="E19">
         <v>6724</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>5502</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>5700</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>5600</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>5919</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>5712</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>5561</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>5624</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>5675</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>5945</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>5925</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>5540</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>5630</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>5920</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>5946</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>5661</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>5551</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>5673</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>5940</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>5609</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>5552</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>5672</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>6917</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>5662</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>5553</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>5650</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>6914</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>5665</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>5674</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>5622</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>6915</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>5664</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>5556</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>5643</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>6916</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>5667</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>5555</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>5641</v>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>6917</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>5752</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>5621</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>5530</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>5820</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>5746</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="n">
+    <row r="12" spans="1:5">
+      <c r="B12">
         <v>5536</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>5811</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>5745</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="n">
+    <row r="13" spans="1:5">
+      <c r="B13">
         <v>5534</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>5800</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>5751</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="n">
+    <row r="14" spans="1:5">
+      <c r="B14">
         <v>5731</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>5668</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>5743</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="n">
+    <row r="15" spans="1:5">
+      <c r="B15">
         <v>5720</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>5830</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>5742</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="n">
+    <row r="16" spans="1:5">
+      <c r="B16">
         <v>5726</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>5837</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="n">
+    </row>
+    <row r="17" spans="2:4">
+      <c r="B17">
         <v>5727</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>5838</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="n">
+    </row>
+    <row r="18" spans="2:4">
+      <c r="B18">
         <v>5732</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="n">
+    </row>
+    <row r="19" spans="2:4">
+      <c r="B19">
         <v>5537</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>5836</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="n">
+    </row>
+    <row r="20" spans="2:4">
+      <c r="B20">
         <v>5725</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="n">
+    </row>
+    <row r="21" spans="2:4">
+      <c r="B21">
         <v>5732</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="n">
+    </row>
+    <row r="22" spans="2:4">
+      <c r="B22">
         <v>5539</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="n">
+    </row>
+    <row r="23" spans="2:4">
+      <c r="B23">
         <v>5538</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>9361</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>9168</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>9461</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>9730</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>9794</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>9371</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>9311</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>9471</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>9739</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>9900</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>9441</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>9300</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>9733</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>9721</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>9909</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>9433</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>9351</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9740</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>9743</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>9921</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>9451</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>9321</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>9632</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>9751</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>9781</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>9481</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>9341</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>9662</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>9611</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>9771</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>9421</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>9363</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>9621</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>9789</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>9912</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>9492</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>9344</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>9641</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>9722</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>9757</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>9362</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>9512</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>9631</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>9723</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>9761</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>9372</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>9643</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>9621</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>9724</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>9795</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12">
         <v>9373</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>9651</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>9462</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>9725</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>9796</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13">
         <v>9442</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>9661</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>9463</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>9726</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>9798</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14">
         <v>9443</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>9664</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>9464</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>9727</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>9922</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15">
         <v>9444</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>9375</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>9472</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>9744</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>9782</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16">
         <v>9434</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>9169</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>9473</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>9745</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>9783</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17">
         <v>9435</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>9312</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>9474</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>9746</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>9784</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18">
         <v>9436</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>9313</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>9475</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>9747</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>9772</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19">
         <v>9437</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>9352</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>9476</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>9748</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>9773</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20">
         <v>9482</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>9353</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>9734</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>9749</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>9774</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21">
         <v>9483</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>9354</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>9735</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>9752</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>9775</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>9484</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>9322</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>9736</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>9753</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>9776</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>9485</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>9323</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>9737</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>9754</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>9777</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>9422</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>9324</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>9738</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>9612</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>9762</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25">
         <v>9423</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>9325</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>9633</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>9790</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>9763</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26">
         <v>9493</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>9326</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>9634</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>9791</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>9764</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:5">
+      <c r="A27">
         <v>9494</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>9341</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>9635</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>9792</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>9765</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:5">
+      <c r="A28">
         <v>9495</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>9342</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>9636</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>9793</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>9766</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:5">
+      <c r="A29">
         <v>9330</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>9343</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>9663</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
         <v>9400</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>9344</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>9622</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="n">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="B31">
         <v>9345</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>9623</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="n">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32">
         <v>9346</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>9624</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="n">
+    </row>
+    <row r="33" spans="2:3">
+      <c r="B33">
         <v>9364</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>9625</v>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="n">
+    </row>
+    <row r="34" spans="2:3">
+      <c r="B34">
         <v>9365</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>9632</v>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="n">
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35">
         <v>9513</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>9633</v>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="n">
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36">
         <v>9514</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>9634</v>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="n">
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37">
         <v>9515</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>9635</v>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="n">
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38">
         <v>9652</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>9636</v>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="n">
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39">
         <v>9653</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>9622</v>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="n">
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40">
         <v>9665</v>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>9171</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>9000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>9700</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>9091</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>9144</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>5141</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>9062</v>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>9082</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>9142</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>9143</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>9063</v>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>9111</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>9145</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>9161</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>9081</v>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>9112</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>9100</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>9153</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>9086</v>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>9123</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>9131</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>9181</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>9071</v>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>8431</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>9121</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>9200</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>9072</v>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>8553</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>9314</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>9231</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>9073</v>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8563</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>9316</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>9241</v>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>8571</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>9315</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>9221</v>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>9092</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>8516</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12">
         <v>9172</v>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>9093</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>8518</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13">
         <v>9173</v>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>9094</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>8533</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14">
         <v>9174</v>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>9095</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>8521</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15">
         <v>9175</v>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>9096</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>8541</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16">
         <v>9176</v>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>9097</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>9132</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17">
         <v>9177</v>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>9098</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>9133</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18">
         <v>9178</v>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>9099</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>9134</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19">
         <v>9162</v>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>9083</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>9135</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20">
         <v>9163</v>
       </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>9084</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>9136</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21">
         <v>9164</v>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>9085</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>9122</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>9165</v>
       </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>8432</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>9123</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>9166</v>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>8433</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>9124</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>9167</v>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>8434</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>9125</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25">
         <v>9168</v>
       </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>8435</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>8522</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26">
         <v>9182</v>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>8436</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>8523</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:5">
+      <c r="A27">
         <v>9183</v>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>8437</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
         <v>9184</v>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>8438</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
         <v>9232</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>8439</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
         <v>9233</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>8554</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
         <v>9234</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>8555</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
         <v>9235</v>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>8556</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
         <v>9242</v>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>8557</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
         <v>9243</v>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>8558</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
         <v>9244</v>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>8564</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
         <v>9245</v>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
         <v>9246</v>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
         <v>9222</v>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
         <v>9223</v>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
         <v>9224</v>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
         <v>9225</v>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
         <v>9226</v>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>9951</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>9944</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>8943</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>8946</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>8824</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>9917</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>9938</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>8983</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>8951</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>8855</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>9931</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>8969</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>8989</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>8876</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>8800</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>8999</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>8960</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>8911</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>8885</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>8832</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>9961</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>8981</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>8921</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>8893</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>8881</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>9970</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>8919</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>9811</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>8771</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>8861</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>9982</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>8990</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>9826</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>8947</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>8825</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>9941</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>8945</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>9913</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8952</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>8826</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>9952</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>8947</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>8944</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>8953</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>8827</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>9953</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>9945</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>8990</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>8954</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>8856</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12">
         <v>9954</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>9946</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>8991</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>8955</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>8857</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13">
         <v>9918</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>8970</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>8992</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>8956</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>8833</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14">
         <v>9919</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>8971</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>8993</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>8957</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>8834</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15">
         <v>9932</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>8972</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>8994</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>8958</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>8835</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16">
         <v>9933</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>8973</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>8995</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>8959</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>8882</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17">
         <v>9934</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>8974</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>8996</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>8877</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>8883</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18">
         <v>9935</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>8975</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>8997</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>8878</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>8862</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19">
         <v>9936</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>8976</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>8998</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>8879</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>8863</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20">
         <v>9937</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>8977</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>8912</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>8886</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>8864</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21">
         <v>9962</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>8978</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>8913</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>8887</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>8865</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>9983</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>8982</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>8914</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>8888</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>8866</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>9942</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>8983</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>9812</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>8889</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>8867</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>9943</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>8984</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>9813</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>8894</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>8868</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="n">
+    <row r="25" spans="1:5">
+      <c r="B25">
         <v>8985</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>9814</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>8895</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>8869</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="n">
+    <row r="26" spans="1:5">
+      <c r="B26">
         <v>8986</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>9914</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>8896</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="n">
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27">
         <v>8987</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>9915</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="n">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="B28">
         <v>8988</v>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="n">
+    </row>
+    <row r="29" spans="1:5">
+      <c r="B29">
         <v>8948</v>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E35"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>8752</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>8943</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>8932</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>8900</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>9800</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>8756</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>8925</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>8934</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>8921</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>9821</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>8821</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>8929</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>8785</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>8923</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>9831</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>8827</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>8935</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>8788</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>8931</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>9833</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>8742</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>8915</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>8351</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>8913</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>8941</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>8391</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>8762</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>8321</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>8924</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>9600</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>8936</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>8741</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8792</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>8914</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>9756</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>8761</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>8782</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>8330</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>9681</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>8771</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>8380</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>9549</v>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>9674</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>8753</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>8354</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>8341</v>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>9822</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12">
         <v>8743</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>8360</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>8352</v>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>9823</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13">
         <v>8744</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>8372</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>8353</v>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>9824</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14">
         <v>8745</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>8311</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>354</v>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>9825</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15">
         <v>8746</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>8926</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>8355</v>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>9834</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16">
         <v>8748</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>8783</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>8356</v>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>9835</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17">
         <v>8749</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>8784</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>8357</v>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>9836</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18">
         <v>8848</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>8373</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>8793</v>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>8942</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19">
         <v>8392</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>8312</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>8794</v>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>9682</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20">
         <v>8762</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>8313</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>8795</v>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>9683</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21">
         <v>8763</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>8314</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>8796</v>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>9684</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>8764</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>8315</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>8797</v>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>9685</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>8765</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>8316</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>8798</v>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>9686</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>8766</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>8317</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>8799</v>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>9675</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25">
         <v>8767</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>8318</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>8342</v>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>9676</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26">
         <v>8768</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>8319</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>8343</v>
       </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
         <v>8769</v>
       </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>8344</v>
       </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
         <v>8772</v>
       </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>8345</v>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
         <v>8773</v>
       </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>8346</v>
       </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
         <v>8774</v>
       </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>8347</v>
       </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
         <v>8775</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>8348</v>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
         <v>8776</v>
       </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>8349</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
         <v>8777</v>
       </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
         <v>8778</v>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
         <v>8779</v>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Hétfő</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Kedd</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Szerda</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Csütörtök</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Péntek</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>8261</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>8475</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>9523</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>8200</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>8440</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:5">
+      <c r="A3">
         <v>8300</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>8348</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>9533</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>8246</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>8581</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:5">
+      <c r="A4">
         <v>8251</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>9541</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>8500</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>8226</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>8420</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:5">
+      <c r="A5">
         <v>8237</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>9673</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>8512</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>8220</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>8109</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:5">
+      <c r="A6">
         <v>8241</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>9551</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>8514</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>8171</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>8413</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:5">
+      <c r="A7">
         <v>8271</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>8491</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>8591</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>8161</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>8441</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:5">
+      <c r="A8">
         <v>8281</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>9561</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8481</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>9191</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>8442</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:5">
+      <c r="A9">
         <v>8291</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>9531</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>8447</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>8191</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>8443</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:5">
+      <c r="A10">
         <v>8308</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>9511</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>8455</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>8105</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>8444</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:5">
+      <c r="A11">
         <v>8452</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>9516</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>8471</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>8100</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>8445</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:5">
+      <c r="A12">
         <v>8409</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>9522</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>8460</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>8247</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>8446</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:5">
+      <c r="A13">
         <v>8262</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>8476</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>8478</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>8248</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>8421</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:5">
+      <c r="A14">
         <v>8263</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>8477</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>8468</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>8227</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>8422</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:5">
+      <c r="A15">
         <v>8264</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>9542</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>9534</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>8228</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>8423</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:5">
+      <c r="A16">
         <v>8265</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>9543</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>9535</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>8229</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>8424</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:5">
+      <c r="A17">
         <v>8252</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>9544</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>8515</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>8230</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>8425</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:5">
+      <c r="A18">
         <v>8253</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>9545</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>8592</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>8231</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>8426</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:5">
+      <c r="A19">
         <v>8254</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>9546</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>8593</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>8232</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>8427</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:5">
+      <c r="A20">
         <v>8255</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>9547</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>8594</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>8233</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>8428</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:5">
+      <c r="A21">
         <v>8256</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>9552</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>8596</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>8172</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>8429</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:5">
+      <c r="A22">
         <v>8242</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>9553</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>8597</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>8173</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>8414</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:5">
+      <c r="A23">
         <v>8243</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>9554</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>8482</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>8174</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>8415</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:5">
+      <c r="A24">
         <v>8244</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>9555</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>8483</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>8175</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>8416</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:5">
+      <c r="A25">
         <v>8245</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>9556</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>8484</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>8162</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>8417</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:5">
+      <c r="A26">
         <v>8272</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>8492</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>8485</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>9192</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
         <v>8273</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>8493</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>8448</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>8192</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
         <v>8274</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>8494</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>8449</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>8193</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
         <v>8275</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>8495</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>8456</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>8194</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
         <v>8282</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>8496</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>8457</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>8195</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
         <v>8283</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>8497</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>8458</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>8196</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
         <v>8284</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>9532</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>8472</v>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>8285</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>9517</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>8473</v>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>8286</v>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>8474</v>
       </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>8292</v>
       </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>8479</v>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>8293</v>
       </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>8294</v>
       </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>8295</v>
       </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>8296</v>
       </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>8297</v>
       </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>8453</v>
       </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>8454</v>
       </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>